--- a/data/trans_dic/KIDMED_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,55</t>
+          <t>0,71; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,68</t>
+          <t>1,6; 9,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,24</t>
+          <t>1,53; 5,89</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>2,33; 11,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 12,26</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,54</t>
+          <t>1,42; 6,43</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,54; 9,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,83</t>
+          <t>0,0; 9,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,13</t>
+          <t>0,75; 6,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,06</t>
+          <t>0,89; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,96</t>
+          <t>2,15; 7,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,83</t>
+          <t>2,01; 5,34</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,57</t>
+          <t>0,57; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,26</t>
+          <t>0,63; 5,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,85</t>
+          <t>0,97; 4,79</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>1,37; 11,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,09</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,82</t>
+          <t>1,15; 6,31</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,75</t>
+          <t>2,09; 4,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,39</t>
+          <t>1,8; 4,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,85</t>
+          <t>2,14; 3,86</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6802</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1476; 8700</t>
+          <t>860; 7202</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>861; 7685</t>
+          <t>1602; 9038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3643; 12405</t>
+          <t>3389; 13041</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>751</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6012</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3623</t>
+          <t>2094; 10334</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2418; 11484</t>
+          <t>0; 3764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2915; 12245</t>
+          <t>2627; 11914</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2684</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>303; 5540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>392; 6129</t>
+          <t>0; 5105</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>810; 6886</t>
+          <t>813; 7343</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12467</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3564; 13066</t>
+          <t>1760; 10515</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1738; 10543</t>
+          <t>3795; 13738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7028; 20692</t>
+          <t>7514; 19980</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5778</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>686; 6429</t>
+          <t>836; 8827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1091; 9987</t>
+          <t>725; 6812</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2895; 13349</t>
+          <t>2528; 12498</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4253</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>901; 7686</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>930; 8347</t>
+          <t>0; 4585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1696; 9405</t>
+          <t>1562; 8601</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>37996</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10874; 24195</t>
+          <t>14134; 29942</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13863; 32124</t>
+          <t>10977; 25345</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30378; 53029</t>
+          <t>27556; 49615</t>
         </is>
       </c>
     </row>
